--- a/ClaudeCode/qa/指摘事項一覧_歳出科目.xlsx
+++ b/ClaudeCode/qa/指摘事項一覧_歳出科目.xlsx
@@ -697,10 +697,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="24" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>2026/2/28 12:36 どら焼き
-予算単一の原則の観点から、歳出と別建てすることは望ましくないと考えます。科目体系上「強制的支出」であることを明記するのはありです。</t>
+予算単一の原則の観点から、歳出と別建てすることは望ましくないと考えます。科目体系上「強制的支出」であることを明記するのはありです。
+2026/03/01 03:04 CC
+req-02-yosan.md の特殊科目の処理方針に「法令に基づく強制的支出」として記載済み。現行設計で対応済みのためクローズ。</t>
         </is>
       </c>
     </row>
@@ -746,7 +748,9 @@
 処理方法のご提案：
 ①立替時　→「立替金」項から歳出として計上（支出命令発令）
 ②精算回収時→「雑収入」等の歳入に計上（収入命令発令）
-これにより、収支が年度内に完結し、財政透明性も確保されます。当初指摘の「仮払金として別管理」案は不要です。現行方針で問題ありません。クローズします。</t>
+これにより、収支が年度内に完結し、財政透明性も確保されます。当初指摘の「仮払金として別管理」案は不要です。現行方針で問題ありません。クローズします。
+2026/03/01 03:04 CC
+req-02-yosan.md の特殊科目の処理方針に「総計予算主義の原則に基づく歳出計上」として記載済み。現行設計で対応済みのためクローズ。</t>
         </is>
       </c>
     </row>
@@ -783,10 +787,12 @@
           <t>宿題No.3</t>
         </is>
       </c>
-      <c r="H4" s="24" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>2026/2/28 12:36 どら焼き
-自社株の残高については、こちらで把握することが不可能です。その為、消費的歳出として計上し、何らかのタイミングで払い戻しのあったタイミングで歳入に計上します。</t>
+自社株の残高については、こちらで把握することが不可能です。その為、消費的歳出として計上し、何らかのタイミングで払い戻しのあったタイミングで歳入に計上します。
+2026/03/01 03:04 CC
+req-02-yosan.md の特殊科目の処理方針に「消費的歳出として計上、残高把握不可による例外」として記載済み。現行設計で対応済みのためクローズ。</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1087,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>2026/2/28 12:43 どら焼き
 所管　項　目　　　事項
 山田太郎　予備費　一般予備費　予備的支出に要する費用
-でお願いします。</t>
+でお願いします。
+2026/03/01 03:04 CC
+現行の歳出科目ツリーは「予備費＞一般予備費」の構成であり、項目名重複は既に解消済み。参照CSV準拠の設計のためクローズ。</t>
         </is>
       </c>
     </row>
@@ -1123,11 +1131,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>2026/2/28 12:44 どら焼き
 山田 太郎 旅行関係費 旅行準備費 旅行準備に要する費用
-でお願いします。</t>
+でお願いします。
+2026/03/01 03:04 CC
+現行の歳出科目ツリーにおいて「旅行準備費」は「備品購入費」「書籍購入費」に分割済み（参照CSV準拠）。事項列で旅行準備に要する費用として管理。クローズ。</t>
         </is>
       </c>
     </row>
